--- a/pmo-hub-project-import-template.xlsx
+++ b/pmo-hub-project-import-template.xlsx
@@ -1,21 +1,45 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
-  <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Projects" sheetId="2" state="visible" r:id="rId2"/>
-  </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties">
+  <Application>Microsoft Excel Compatible / Openpyxl 3.1.5</Application>
+  <AppVersion>3.1</AppVersion>
+</Properties>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties">
+  <dc:creator xmlns:dc="http://purl.org/dc/elements/1.1/">openpyxl</dc:creator>
+  <dcterms:created xmlns:dcterms="http://purl.org/dc/terms/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xsi:type="dcterms:W3CDTF">2026-07-30T20:08:50Z</dcterms:created>
+  <dcterms:modified xmlns:dcterms="http://purl.org/dc/terms/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xsi:type="dcterms:W3CDTF">2026-08-03T23:53:28Z</dcterms:modified>
+</cp:coreProperties>
+</file>
+
+<file path=xl\comments\comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>PMO Hub</author>
+  </authors>
+  <commentList>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Leave this blank in almost every case -- PMO Hub derives Backlog/Planned/Active automatically from Start Date and Target End Date. Only enter Hold or Complete here, to mark a project as already paused or finished (something dates alone can not show).</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>If this email matches an existing PMO Hub account, the project will be linked to that person for permissions. Otherwise it is shown as text only.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>If this email matches an existing PMO Hub account, the project will be linked to that person for permissions. Otherwise it's shown as text only.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
   <fonts count="5">
@@ -161,32 +185,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>PMO Hub</author>
-  </authors>
-  <commentList>
-    <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t>Leave this blank in almost every case -- PMO Hub derives Backlog/Planned/Active automatically from Start Date and Target End Date. Only enter Hold or Complete here, to mark a project as already paused or finished (something dates alone can not show).</t>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t>If this email matches an existing PMO Hub account, the project will be linked to that person for permissions. Otherwise it is shown as text only.</t>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t>If this email matches an existing PMO Hub account, the project will be linked to that person for permissions. Otherwise it's shown as text only.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -469,7 +468,23 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
+  <sheets>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Projects" sheetId="2" state="visible" r:id="rId2"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -515,7 +530,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>3. Columns with a dropdown arrow (Business Unit, Status, Phase, Priority, Value Area)</t>
+          <t>3. Columns with a dropdown arrow (Business Unit, Status, Phase, Value Area)</t>
         </is>
       </c>
     </row>
@@ -623,13 +638,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -640,14 +655,13 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -693,40 +707,35 @@
       </c>
       <c r="I1" s="3" t="inlineStr">
         <is>
-          <t>Priority</t>
+          <t>Value Area</t>
         </is>
       </c>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Value Area</t>
+          <t>Start Date</t>
         </is>
       </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
-          <t>Start Date</t>
+          <t>Target End Date</t>
         </is>
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
-          <t>Target End Date</t>
+          <t>Progress %</t>
         </is>
       </c>
       <c r="M1" s="3" t="inlineStr">
         <is>
-          <t>Progress %</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="N1" s="3" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Current Blockers</t>
         </is>
       </c>
       <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>Current Blockers</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>Tags</t>
         </is>
@@ -770,45 +779,40 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Operational Efficiency</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>Operational Efficiency</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="M2" s="4" t="n">
+      <c r="L2" s="4" t="n">
         <v>35</v>
       </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>Automating pallet routing in the East distribution center.</t>
+        </is>
+      </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>Automating pallet routing in the East distribution center.</t>
+          <t>Waiting on hardware vendor lead time</t>
         </is>
       </c>
       <c r="O2" s="4" t="inlineStr">
         <is>
-          <t>Waiting on hardware vendor lead time</t>
-        </is>
-      </c>
-      <c r="P2" s="4" t="inlineStr">
-        <is>
           <t>Supply Chain, CRM System</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="6">
+  <dataValidations count="5">
     <dataValidation sqref="E3:E500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Customer Experience,Finance,Legal &amp; Compliance,Marketing,Operations,Product,Sales,Supply Chain,Technology"</formula1>
     </dataValidation>
@@ -819,9 +823,6 @@
       <formula1>"Not Started,On Track,At Risk,Planning,Blocked,Complete"</formula1>
     </dataValidation>
     <dataValidation sqref="I3:I500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Critical,High,Medium,Low,Needs prioritization"</formula1>
-    </dataValidation>
-    <dataValidation sqref="J3:J500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Revenue Growth,Customer Experience,Operational Efficiency,Employee Experience,Compliance &amp; Risk"</formula1>
     </dataValidation>
     <dataValidation sqref="H3:H500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
